--- a/exports/LICHSGFIN_full_report.xlsx
+++ b/exports/LICHSGFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.36</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>369.45</v>
+        <v>361.7</v>
       </c>
       <c r="I2" t="n">
         <v>364.5836937779073</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.22</v>
+        <v>-2.31</v>
       </c>
       <c r="L2" t="n">
-        <v>1.13</v>
+        <v>3.12</v>
       </c>
       <c r="M2" t="n">
         <v>0.04</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>6.73</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>338.2</v>
+        <v>385.6</v>
       </c>
       <c r="I3" t="n">
         <v>353.2094595764017</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>6.5</v>
+        <v>-6.61</v>
       </c>
       <c r="L3" t="n">
-        <v>2.31</v>
+        <v>7.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.41</v>
+        <v>3.62</v>
       </c>
       <c r="N3" t="n">
-        <v>1.41</v>
+        <v>11.41</v>
       </c>
       <c r="O3" t="n">
         <v>-1.95</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>14.91</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>382.45</v>
+        <v>357</v>
       </c>
       <c r="I4" t="n">
         <v>367.4840734312439</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.82</v>
+        <v>-7.42</v>
       </c>
       <c r="L4" t="n">
         <v>9.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>8.73</v>
       </c>
       <c r="O4" t="n">
         <v>11.41</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.27</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>337.1</v>
+        <v>351.7</v>
       </c>
       <c r="I5" t="n">
         <v>350.396102377062</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>5.57</v>
+        <v>1.48</v>
       </c>
       <c r="L5" t="n">
         <v>9.619999999999999</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>366.35</v>
+        <v>360.45</v>
       </c>
       <c r="I6" t="n">
         <v>364.0855516640128</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K6" t="n">
-        <v>4.17</v>
+        <v>2.49</v>
       </c>
       <c r="L6" t="n">
         <v>2.9</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.99</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44683.38541666666</v>
+        <v>44683.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>371.7</v>
+        <v>381.35</v>
       </c>
       <c r="I7" t="n">
         <v>380.9984433537852</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.12</v>
+        <v>-5.8</v>
       </c>
       <c r="L7" t="n">
         <v>6.92</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>8.26</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>360.45</v>
+        <v>350.1</v>
       </c>
       <c r="I8" t="n">
         <v>353.2867659529241</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.48</v>
+        <v>-8.19</v>
       </c>
       <c r="L8" t="n">
-        <v>6.04</v>
+        <v>8.85</v>
       </c>
       <c r="M8" t="n">
-        <v>-0</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
         <v>5.34</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>347.9</v>
+        <v>359.45</v>
       </c>
       <c r="I9" t="n">
         <v>353.5090544717764</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>0.63</v>
+        <v>-2.67</v>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>4.51</v>
       </c>
       <c r="M9" t="n">
-        <v>1.55</v>
+        <v>2.39</v>
       </c>
       <c r="N9" t="n">
         <v>4.72</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>9.1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>365.2</v>
+        <v>351.25</v>
       </c>
       <c r="I10" t="n">
         <v>352.2982013928773</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6</v>
+        <v>-2.28</v>
       </c>
       <c r="L10" t="n">
-        <v>1.22</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.36</v>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>4.31</v>
       </c>
       <c r="O10" t="n">
         <v>3.68</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.01</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44736.38541666666</v>
+        <v>44736.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>309.3</v>
+        <v>312</v>
       </c>
       <c r="I11" t="n">
         <v>310.1911611305614</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>11.94</v>
+        <v>11.17</v>
       </c>
       <c r="L11" t="n">
         <v>3.07</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.05</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44777.38541666666</v>
+        <v>44777.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>364.8</v>
+        <v>363</v>
       </c>
       <c r="I12" t="n">
         <v>364.7614158480844</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>40.83333333333334</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>16.92</v>
+        <v>16.35</v>
       </c>
       <c r="L12" t="n">
         <v>1.19</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.98</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44789.55208333334</v>
+        <v>44790.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>384.2</v>
+        <v>389.75</v>
       </c>
       <c r="I13" t="n">
         <v>388.3298875620719</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.84</v>
+        <v>-7.37</v>
       </c>
       <c r="L13" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="M13" t="n">
         <v>2.75</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.27</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>421.5</v>
+        <v>409.6</v>
       </c>
       <c r="I14" t="n">
         <v>416.5074500875928</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K14" t="n">
-        <v>8.15</v>
+        <v>5.09</v>
       </c>
       <c r="L14" t="n">
         <v>6.22</v>
@@ -1239,7 +1406,7 @@
         <v>3.02</v>
       </c>
       <c r="N14" t="n">
-        <v>2.89</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
         <v>0.6899999999999999</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.44</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>409.45</v>
+        <v>416.45</v>
       </c>
       <c r="I15" t="n">
         <v>409.7109782363337</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>0.04</v>
+        <v>-1.67</v>
       </c>
       <c r="L15" t="n">
         <v>2.51</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.06</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44865.55208333334</v>
+        <v>44866.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="I16" t="n">
         <v>393.6953314464955</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.67</v>
+        <v>-5.63</v>
       </c>
       <c r="L16" t="n">
         <v>5.94</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44890.55208333334</v>
+        <v>44893.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>375</v>
+        <v>378.4</v>
       </c>
       <c r="I17" t="n">
         <v>377.5626668960983</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n">
-        <v>4.58</v>
+        <v>3.72</v>
       </c>
       <c r="L17" t="n">
         <v>1.72</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.88</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44918.38541666666</v>
+        <v>44918.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>394.15</v>
+        <v>389.55</v>
       </c>
       <c r="I18" t="n">
         <v>391.4618570075094</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>4.16</v>
+        <v>2.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.36</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.54</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>413.7</v>
+        <v>415.85</v>
       </c>
       <c r="I19" t="n">
         <v>415.0439555665953</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.2</v>
+        <v>-6.75</v>
       </c>
       <c r="L19" t="n">
         <v>6.97</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>6.15</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44935.55208333334</v>
+        <v>44936.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>393.5</v>
+        <v>385.9</v>
       </c>
       <c r="I20" t="n">
         <v>393.4964478853748</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.37</v>
+        <v>-7.2</v>
       </c>
       <c r="L20" t="n">
-        <v>5.69</v>
+        <v>7.47</v>
       </c>
       <c r="M20" t="n">
         <v>0.04</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.66</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>323.15</v>
+        <v>325.5</v>
       </c>
       <c r="I21" t="n">
         <v>324.7557114309511</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>83</v>
+        <v>83.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>16.26</v>
+        <v>15.65</v>
       </c>
       <c r="L21" t="n">
         <v>3.94</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>5</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>386.85</v>
+        <v>358.05</v>
       </c>
       <c r="I22" t="n">
         <v>366.6920200386081</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>18.85</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
         <v>3.03</v>
       </c>
       <c r="M22" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>1.67</v>
+        <v>6.32</v>
       </c>
       <c r="O22" t="n">
         <v>1.72</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>10.68</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45092.55208333334</v>
+        <v>45093.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>368.05</v>
+        <v>381.3</v>
       </c>
       <c r="I23" t="n">
         <v>371.0102381614439</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.79</v>
+        <v>-6.49</v>
       </c>
       <c r="L23" t="n">
-        <v>6.83</v>
+        <v>7.37</v>
       </c>
       <c r="M23" t="n">
         <v>0.68</v>
       </c>
       <c r="N23" t="n">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="O23" t="n">
         <v>-6.32</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.99</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45124.55208333334</v>
+        <v>45125.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>381.7</v>
+        <v>378.35</v>
       </c>
       <c r="I24" t="n">
         <v>379.0172304312875</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1</v>
+        <v>-0.77</v>
       </c>
       <c r="L24" t="n">
         <v>3.34</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>5.75</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>388.5</v>
+        <v>400.7</v>
       </c>
       <c r="I25" t="n">
         <v>392.3472970185335</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.68</v>
+        <v>-5.91</v>
       </c>
       <c r="L25" t="n">
-        <v>3.48</v>
+        <v>7.02</v>
       </c>
       <c r="M25" t="n">
         <v>0.46</v>
       </c>
       <c r="N25" t="n">
-        <v>1.19</v>
+        <v>3.99</v>
       </c>
       <c r="O25" t="n">
         <v>-1.47</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>5.13</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>405.7</v>
+        <v>392.8</v>
       </c>
       <c r="I26" t="n">
         <v>393.2629571329119</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>1.25</v>
+        <v>-1.97</v>
       </c>
       <c r="L26" t="n">
-        <v>2.99</v>
+        <v>3.53</v>
       </c>
       <c r="M26" t="n">
         <v>0.26</v>
       </c>
       <c r="N26" t="n">
-        <v>0.93</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>3.99</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.61</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45141.55208333334</v>
+        <v>45142.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>391.5</v>
+        <v>420.5</v>
       </c>
       <c r="I27" t="n">
         <v>412.1980276925868</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0.33</v>
+        <v>-7.05</v>
       </c>
       <c r="L27" t="n">
-        <v>4.96</v>
+        <v>7.94</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="O27" t="n">
         <v>-3.5</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.46</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>459.55</v>
+        <v>454.55</v>
       </c>
       <c r="I28" t="n">
         <v>457.5264266484396</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>77.16666666666667</v>
+        <v>80</v>
       </c>
       <c r="K28" t="n">
-        <v>9.289999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="L28" t="n">
         <v>9.27</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>4.68</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>449.55</v>
+        <v>462.25</v>
       </c>
       <c r="I29" t="n">
         <v>460.6674429247155</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>1.1</v>
+        <v>-1.69</v>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="M29" t="n">
         <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
         <v>-2.08</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.64</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>527.3</v>
+        <v>512.1</v>
       </c>
       <c r="I30" t="n">
         <v>514.5498997119475</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>14.07</v>
+        <v>10.78</v>
       </c>
       <c r="L30" t="n">
         <v>3.95</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>6.66</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45289.55208333334</v>
+        <v>45292.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>536.5</v>
+        <v>558.55</v>
       </c>
       <c r="I31" t="n">
         <v>539.0211097663135</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.76</v>
+        <v>-9.07</v>
       </c>
       <c r="L31" t="n">
-        <v>5.45</v>
+        <v>9.42</v>
       </c>
       <c r="M31" t="n">
         <v>0.85</v>
       </c>
       <c r="N31" t="n">
-        <v>1.8</v>
+        <v>4.29</v>
       </c>
       <c r="O31" t="n">
         <v>-3.36</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.65</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>634.8</v>
+        <v>624.05</v>
       </c>
       <c r="I32" t="n">
         <v>633.4582916746518</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>70.16666666666667</v>
+        <v>71</v>
       </c>
       <c r="K32" t="n">
-        <v>13.65</v>
+        <v>11.73</v>
       </c>
       <c r="L32" t="n">
         <v>3.63</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.46</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>590</v>
+        <v>606.7</v>
       </c>
       <c r="I33" t="n">
         <v>604.4959541700916</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K33" t="n">
-        <v>5.46</v>
+        <v>2.78</v>
       </c>
       <c r="L33" t="n">
         <v>2.4</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.2</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>652.8</v>
+        <v>632.15</v>
       </c>
       <c r="I34" t="n">
         <v>637.3544200027724</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K34" t="n">
-        <v>7.6</v>
+        <v>4.19</v>
       </c>
       <c r="L34" t="n">
         <v>2.46</v>
@@ -2379,7 +2786,7 @@
         <v>2.57</v>
       </c>
       <c r="N34" t="n">
-        <v>2.42</v>
+        <v>3.16</v>
       </c>
       <c r="O34" t="n">
         <v>3.95</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.74</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>634</v>
+        <v>674.65</v>
       </c>
       <c r="I35" t="n">
         <v>662.0966165953142</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.29</v>
+        <v>-6.72</v>
       </c>
       <c r="L35" t="n">
-        <v>5.98</v>
+        <v>6.99</v>
       </c>
       <c r="M35" t="n">
-        <v>1.57</v>
+        <v>5.68</v>
       </c>
       <c r="N35" t="n">
-        <v>4.82</v>
+        <v>7.05</v>
       </c>
       <c r="O35" t="n">
         <v>-3.16</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.95</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>678.7</v>
+        <v>588.55</v>
       </c>
       <c r="I36" t="n">
         <v>634.7153142651042</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6</v>
+        <v>-12.76</v>
       </c>
       <c r="L36" t="n">
-        <v>3.42</v>
+        <v>19.25</v>
       </c>
       <c r="M36" t="n">
-        <v>-0</v>
+        <v>0.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>14.48</v>
       </c>
       <c r="O36" t="n">
         <v>7.05</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>17.06</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>660.45</v>
+        <v>674.5</v>
       </c>
       <c r="I37" t="n">
         <v>673.6628454452656</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>-12.22</v>
+        <v>-14.6</v>
       </c>
       <c r="L37" t="n">
-        <v>14.68</v>
+        <v>15.2</v>
       </c>
       <c r="M37" t="n">
         <v>2.17</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>10.81</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45497.55208333334</v>
+        <v>45498.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>786</v>
+        <v>760.25</v>
       </c>
       <c r="I38" t="n">
         <v>764.3339315785046</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K38" t="n">
-        <v>16.53</v>
+        <v>12.71</v>
       </c>
       <c r="L38" t="n">
         <v>1.7</v>
       </c>
       <c r="M38" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="N38" t="n">
         <v>3.46</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45538.38541666666</v>
+        <v>45538.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>684.35</v>
+        <v>694</v>
       </c>
       <c r="I39" t="n">
         <v>689.1766107488415</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K39" t="n">
-        <v>9.98</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L39" t="n">
         <v>6.48</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>5.38</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>674.9</v>
+        <v>652.4</v>
       </c>
       <c r="I40" t="n">
         <v>674.8281291202636</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.75</v>
+        <v>-5.99</v>
       </c>
       <c r="L40" t="n">
-        <v>3.46</v>
+        <v>7.2</v>
       </c>
       <c r="M40" t="n">
         <v>0.6</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.93</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45593.55208333334</v>
+        <v>45594.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>618.05</v>
+        <v>630.05</v>
       </c>
       <c r="I41" t="n">
         <v>624.0526601380054</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K41" t="n">
-        <v>5.27</v>
+        <v>3.43</v>
       </c>
       <c r="L41" t="n">
         <v>5.74</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="N41" t="n">
-        <v>3.03</v>
+        <v>3.88</v>
       </c>
       <c r="O41" t="n">
         <v>-1.32</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.41</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>626</v>
+        <v>610.85</v>
       </c>
       <c r="I42" t="n">
         <v>615.8166496453993</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.64</v>
+        <v>-3.05</v>
       </c>
       <c r="L42" t="n">
         <v>4.71</v>
@@ -2835,7 +3338,7 @@
         <v>0.32</v>
       </c>
       <c r="N42" t="n">
-        <v>1.89</v>
+        <v>3.21</v>
       </c>
       <c r="O42" t="n">
         <v>3.88</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.42</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>606</v>
+        <v>615.6</v>
       </c>
       <c r="I43" t="n">
         <v>614.8781426025412</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>0.79</v>
+        <v>-0.78</v>
       </c>
       <c r="L43" t="n">
         <v>2.72</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>4.66</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45663.55208333334</v>
+        <v>45664.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>592.55</v>
+        <v>584.55</v>
       </c>
       <c r="I44" t="n">
         <v>587.4164268190352</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.74</v>
+        <v>-5.04</v>
       </c>
       <c r="L44" t="n">
-        <v>4.13</v>
+        <v>5.87</v>
       </c>
       <c r="M44" t="n">
         <v>-0</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>562.95</v>
+        <v>573.2</v>
       </c>
       <c r="I45" t="n">
         <v>570.8470515045682</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>3.7</v>
+        <v>1.94</v>
       </c>
       <c r="L45" t="n">
         <v>2.34</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.58</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>561.65</v>
+        <v>543.2</v>
       </c>
       <c r="I46" t="n">
         <v>556.2178686190285</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.02</v>
+        <v>-5.23</v>
       </c>
       <c r="L46" t="n">
-        <v>4.82</v>
+        <v>5.26</v>
       </c>
       <c r="M46" t="n">
         <v>0.93</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>9.1</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>521.5</v>
+        <v>530.75</v>
       </c>
       <c r="I47" t="n">
         <v>526.9864401241356</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
-        <v>3.99</v>
+        <v>2.29</v>
       </c>
       <c r="L47" t="n">
         <v>3.98</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="N47" t="n">
         <v>3.76</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.62</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>563.45</v>
+        <v>538.5</v>
       </c>
       <c r="I48" t="n">
         <v>547.4387615413485</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K48" t="n">
-        <v>6.16</v>
+        <v>1.46</v>
       </c>
       <c r="L48" t="n">
         <v>3.05</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3</v>
+        <v>5.23</v>
       </c>
       <c r="N48" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
         <v>1.44</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.65</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>558.95</v>
+        <v>581.6</v>
       </c>
       <c r="I49" t="n">
         <v>574.3011482764798</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.8</v>
+        <v>-8</v>
       </c>
       <c r="L49" t="n">
-        <v>7.11</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M49" t="n">
         <v>2.12</v>
       </c>
       <c r="N49" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="O49" t="n">
         <v>-2.6</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.85</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>587.3</v>
+        <v>574.5</v>
       </c>
       <c r="I50" t="n">
         <v>583.493799213306</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>0.98</v>
+        <v>-1.22</v>
       </c>
       <c r="L50" t="n">
         <v>3.19</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>7.72</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>602.1</v>
+        <v>611.3</v>
       </c>
       <c r="I51" t="n">
         <v>607.902578821935</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.8</v>
+        <v>-6.41</v>
       </c>
       <c r="L51" t="n">
-        <v>5.15</v>
+        <v>7.4</v>
       </c>
       <c r="M51" t="n">
         <v>2.84</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.28</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>602</v>
+        <v>581.15</v>
       </c>
       <c r="I52" t="n">
         <v>596.3837130646913</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.52</v>
+        <v>-4.93</v>
       </c>
       <c r="L52" t="n">
-        <v>4.55</v>
+        <v>5.26</v>
       </c>
       <c r="M52" t="n">
         <v>2.6</v>
       </c>
       <c r="N52" t="n">
-        <v>3.04</v>
+        <v>3.49</v>
       </c>
       <c r="O52" t="n">
         <v>0.22</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>7.21</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>604</v>
+        <v>612.95</v>
       </c>
       <c r="I53" t="n">
         <v>612.4104656933947</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.93</v>
+        <v>-5.47</v>
       </c>
       <c r="L53" t="n">
-        <v>5.12</v>
+        <v>5.64</v>
       </c>
       <c r="M53" t="n">
         <v>1.51</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.75</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45860.55208333334</v>
+        <v>45861.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>620</v>
+        <v>612.8</v>
       </c>
       <c r="I54" t="n">
         <v>617.3804486783841</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>1.15</v>
+        <v>-0.02</v>
       </c>
       <c r="L54" t="n">
         <v>2.35</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.74</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45912.55208333334</v>
+        <v>45915.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>567.3</v>
+        <v>572.7</v>
       </c>
       <c r="I55" t="n">
         <v>571.1335660089313</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K55" t="n">
-        <v>7.42</v>
+        <v>6.54</v>
       </c>
       <c r="L55" t="n">
         <v>1.72</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>3.21</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>575.1</v>
+        <v>573.45</v>
       </c>
       <c r="I56" t="n">
         <v>574.7586337651641</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="L56" t="n">
         <v>1.2</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>3.33</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45953.55208333334</v>
+        <v>45954.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>580</v>
+        <v>581.5</v>
       </c>
       <c r="I57" t="n">
         <v>581.2913653221459</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.14</v>
+        <v>-1.4</v>
       </c>
       <c r="L57" t="n">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="M57" t="n">
         <v>0.63</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>2.78</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45959.55208333334</v>
+        <v>45960.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>593.9</v>
+        <v>568.25</v>
       </c>
       <c r="I58" t="n">
         <v>574.6747233673724</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K58" t="n">
-        <v>2.13</v>
+        <v>-2.28</v>
       </c>
       <c r="L58" t="n">
-        <v>0.63</v>
+        <v>2.63</v>
       </c>
       <c r="M58" t="n">
-        <v>-0</v>
+        <v>0.15</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O58" t="n">
         <v>0.09</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.47</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>536</v>
+        <v>545.25</v>
       </c>
       <c r="I59" t="n">
         <v>542.5494663227098</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K59" t="n">
-        <v>5.68</v>
+        <v>4.05</v>
       </c>
       <c r="L59" t="n">
         <v>4.59</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>3.57</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>538</v>
+        <v>527.5</v>
       </c>
       <c r="I60" t="n">
         <v>529.0867507211492</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.33</v>
+        <v>-3.26</v>
       </c>
       <c r="L60" t="n">
-        <v>2.12</v>
+        <v>3.51</v>
       </c>
       <c r="M60" t="n">
         <v>0.2</v>
       </c>
       <c r="N60" t="n">
-        <v>1.09</v>
+        <v>2.57</v>
       </c>
       <c r="O60" t="n">
         <v>1.81</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.8</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46076.55208333334</v>
+        <v>46077.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>524.5</v>
+        <v>529.25</v>
       </c>
       <c r="I61" t="n">
         <v>527.1706013799618</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K61" t="n">
-        <v>0.57</v>
+        <v>-0.33</v>
       </c>
       <c r="L61" t="n">
         <v>2.75</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>4.82</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>527.55</v>
+        <v>515.95</v>
       </c>
       <c r="I62" t="n">
         <v>520.1423131252971</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.32</v>
+        <v>-2.51</v>
       </c>
       <c r="L62" t="n">
-        <v>1.45</v>
+        <v>3.42</v>
       </c>
       <c r="M62" t="n">
         <v>3.14</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.09</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>477.35</v>
+        <v>496.45</v>
       </c>
       <c r="I63" t="n">
         <v>495.4845545768879</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>7.48</v>
+        <v>3.78</v>
       </c>
       <c r="L63" t="n">
         <v>1.94</v>
@@ -4032,7 +4787,7 @@
         <v>1.76</v>
       </c>
       <c r="N63" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
       <c r="O63" t="n">
         <v>-2.19</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.49</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46156.55208333334</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>562</v>
+        <v>554.05</v>
       </c>
       <c r="I64" t="n">
         <v>557.415325295867</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K64" t="n">
-        <v>13.2</v>
+        <v>11.6</v>
       </c>
       <c r="L64" t="n">
         <v>2.7</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.49</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>558.5</v>
+        <v>562.2</v>
       </c>
       <c r="I65" t="n">
         <v>559.0438161490188</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.8</v>
+        <v>-1.47</v>
       </c>
       <c r="L65" t="n">
-        <v>1.97</v>
+        <v>3.01</v>
       </c>
       <c r="M65" t="n">
         <v>1.07</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>4.66</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>540.65</v>
+        <v>530.9</v>
       </c>
       <c r="I66" t="n">
         <v>537.9542485153389</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.83</v>
+        <v>-5.57</v>
       </c>
       <c r="L66" t="n">
-        <v>4.29</v>
+        <v>6.08</v>
       </c>
       <c r="M66" t="n">
         <v>0.28</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.11</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>505.1</v>
+        <v>521.7</v>
       </c>
       <c r="I67" t="n">
         <v>508.8427333414596</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>4.86</v>
+        <v>1.73</v>
       </c>
       <c r="L67" t="n">
         <v>6.05</v>
@@ -4260,7 +5063,7 @@
         <v>0.99</v>
       </c>
       <c r="N67" t="n">
-        <v>2.87</v>
+        <v>4.07</v>
       </c>
       <c r="O67" t="n">
         <v>-2.21</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.13</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46295.38541666666</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>544.8</v>
+        <v>533.5</v>
       </c>
       <c r="I68" t="n">
         <v>539.8759345162347</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K68" t="n">
-        <v>4.43</v>
+        <v>2.26</v>
       </c>
       <c r="L68" t="n">
         <v>3.01</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>7.7</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>516.2</v>
+        <v>535.6</v>
       </c>
       <c r="I69" t="n">
         <v>535.3032243343463</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>3.24</v>
+        <v>-0.39</v>
       </c>
       <c r="L69" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="M69" t="n">
         <v>0.88</v>
       </c>
       <c r="N69" t="n">
-        <v>3.03</v>
+        <v>3.93</v>
       </c>
       <c r="O69" t="n">
         <v>-4.39</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.73</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46310.55208333334</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>534.8</v>
+        <v>521.9</v>
       </c>
       <c r="I70" t="n">
         <v>526.3681002879023</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.15</v>
+        <v>-2.56</v>
       </c>
       <c r="L70" t="n">
         <v>3.02</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>16</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.1</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7512,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7522,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7532,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.59999999999999</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.22</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.56</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.85</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60.9</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.01</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7612,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.68</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.51</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.09</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.210000000000001</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
